--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4249,7 +4249,7 @@
     <t>极雀战靴</t>
   </si>
   <si>
-    <t>血怨魔刃</t>
+    <t>血怨魔刀</t>
   </si>
   <si>
     <t>深渊魔器</t>
@@ -4276,10 +4276,10 @@
     <t>血怨魔靴</t>
   </si>
   <si>
-    <t>碎魂魔刃</t>
-  </si>
-  <si>
-    <t>碎魂魔甲</t>
+    <t>碎魂魔杖</t>
+  </si>
+  <si>
+    <t>碎魂魔衣</t>
   </si>
   <si>
     <t>碎魂魔链</t>
@@ -4300,10 +4300,10 @@
     <t>碎魂魔靴</t>
   </si>
   <si>
-    <t>哀嚎魔刃</t>
-  </si>
-  <si>
-    <t>哀嚎魔甲</t>
+    <t>哀嚎魔剑</t>
+  </si>
+  <si>
+    <t>哀嚎魔袍</t>
   </si>
   <si>
     <t>哀嚎魔链</t>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -469,7 +469,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="1303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="1308">
   <si>
     <t>_Id</t>
   </si>
@@ -4517,6 +4517,21 @@
   </si>
   <si>
     <t>道戒之源</t>
+  </si>
+  <si>
+    <t>神宠契约</t>
+  </si>
+  <si>
+    <t>仙宠契约</t>
+  </si>
+  <si>
+    <t>坐骑契约</t>
+  </si>
+  <si>
+    <t>英灵契约</t>
+  </si>
+  <si>
+    <t>深渊契约</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -4855,12 +4870,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -7097,7 +7112,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M44"/>
+  <dimension ref="C1:M49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="9.625" customWidth="1"/>
@@ -8257,6 +8272,136 @@
       </c>
       <c r="J44" s="2">
         <v>7</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:13">
+      <c r="C45" s="2">
+        <v>180046</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E45" s="2">
+        <v>18</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1</v>
+      </c>
+      <c r="H45" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:13">
+      <c r="C46" s="2">
+        <v>180047</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E46" s="2">
+        <v>18</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G46" s="3">
+        <v>1</v>
+      </c>
+      <c r="H46" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:13">
+      <c r="C47" s="2">
+        <v>180048</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E47" s="2">
+        <v>18</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1</v>
+      </c>
+      <c r="H47" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:13">
+      <c r="C48" s="2">
+        <v>180049</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E48" s="2">
+        <v>18</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1</v>
+      </c>
+      <c r="H48" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:10">
+      <c r="C49" s="2">
+        <v>180050</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E49" s="2">
+        <v>18</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1</v>
+      </c>
+      <c r="H49" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -8403,13 +8548,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -8429,13 +8574,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -8455,13 +8600,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -8481,13 +8626,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -8507,13 +8652,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -8533,13 +8678,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -8561,13 +8706,13 @@
         <v>190007</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="E12" s="2">
         <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -8589,13 +8734,13 @@
         <v>190008</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
       <c r="E13" s="2">
         <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -8617,13 +8762,13 @@
         <v>190009</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="E14" s="2">
         <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -8645,13 +8790,13 @@
         <v>190010</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="E15" s="2">
         <v>19</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -8673,13 +8818,13 @@
         <v>190011</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="E16" s="2">
         <v>19</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -8701,13 +8846,13 @@
         <v>190012</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="E17" s="2">
         <v>19</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -8729,13 +8874,13 @@
         <v>190013</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="E18" s="2">
         <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -8757,13 +8902,13 @@
         <v>190014</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
       <c r="E19" s="2">
         <v>19</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -8785,13 +8930,13 @@
         <v>190015</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
       <c r="E20" s="2">
         <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -8813,13 +8958,13 @@
         <v>190016</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="E21" s="2">
         <v>19</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -8841,13 +8986,13 @@
         <v>190017</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -8869,13 +9014,13 @@
         <v>190018</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
       <c r="E23" s="2">
         <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="9"/>
+    <workbookView windowHeight="17680" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -469,7 +469,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="1308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2498" uniqueCount="1315">
   <si>
     <t>_Id</t>
   </si>
@@ -4010,6 +4010,27 @@
   </si>
   <si>
     <t>三五阶升阶石</t>
+  </si>
+  <si>
+    <t>三六阶升阶石</t>
+  </si>
+  <si>
+    <t>三七阶升阶石</t>
+  </si>
+  <si>
+    <t>三八阶升阶石</t>
+  </si>
+  <si>
+    <t>三九阶升阶石</t>
+  </si>
+  <si>
+    <t>四十阶升阶石</t>
+  </si>
+  <si>
+    <t>四一阶升阶石</t>
+  </si>
+  <si>
+    <t>四二阶升阶石</t>
   </si>
   <si>
     <t>攻击宝石</t>
@@ -7238,13 +7259,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -7264,13 +7285,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1247</v>
+        <v>1254</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7290,13 +7311,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1248</v>
+        <v>1255</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7316,13 +7337,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7342,13 +7363,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -7368,13 +7389,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1251</v>
+        <v>1258</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -7396,13 +7417,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -7424,13 +7445,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1253</v>
+        <v>1260</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -7452,13 +7473,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1254</v>
+        <v>1261</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -7480,13 +7501,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1255</v>
+        <v>1262</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -7508,13 +7529,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -7536,13 +7557,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1257</v>
+        <v>1264</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -7564,13 +7585,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1258</v>
+        <v>1265</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -7592,13 +7613,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1259</v>
+        <v>1266</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -7620,13 +7641,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1260</v>
+        <v>1267</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -7648,13 +7669,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -7676,13 +7697,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -7704,13 +7725,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -7732,13 +7753,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -7760,13 +7781,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1265</v>
+        <v>1272</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -7788,13 +7809,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1266</v>
+        <v>1273</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -7816,13 +7837,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1267</v>
+        <v>1274</v>
       </c>
       <c r="E27" s="2">
         <v>18</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -7849,13 +7870,13 @@
         <v>180030</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1268</v>
+        <v>1275</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -7877,13 +7898,13 @@
         <v>180031</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -7903,13 +7924,13 @@
         <v>180032</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -7929,13 +7950,13 @@
         <v>180033</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1271</v>
+        <v>1278</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -7955,13 +7976,13 @@
         <v>180034</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1272</v>
+        <v>1279</v>
       </c>
       <c r="E33" s="2">
         <v>18</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -7983,13 +8004,13 @@
         <v>180035</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1273</v>
+        <v>1280</v>
       </c>
       <c r="E34" s="2">
         <v>18</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -8011,13 +8032,13 @@
         <v>180036</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1274</v>
+        <v>1281</v>
       </c>
       <c r="E35" s="2">
         <v>18</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -8039,13 +8060,13 @@
         <v>180037</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1275</v>
+        <v>1282</v>
       </c>
       <c r="E36" s="2">
         <v>18</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -8067,13 +8088,13 @@
         <v>180038</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>1276</v>
+        <v>1283</v>
       </c>
       <c r="E37" s="2">
         <v>18</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G37" s="3">
         <v>1</v>
@@ -8095,13 +8116,13 @@
         <v>180039</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1277</v>
+        <v>1284</v>
       </c>
       <c r="E38" s="2">
         <v>18</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -8123,13 +8144,13 @@
         <v>180040</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>1278</v>
+        <v>1285</v>
       </c>
       <c r="E39" s="2">
         <v>18</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G39" s="3">
         <v>1</v>
@@ -8149,13 +8170,13 @@
         <v>180041</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>1279</v>
+        <v>1286</v>
       </c>
       <c r="E40" s="2">
         <v>18</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G40" s="3">
         <v>1</v>
@@ -8175,13 +8196,13 @@
         <v>180042</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1280</v>
+        <v>1287</v>
       </c>
       <c r="E41" s="2">
         <v>18</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G41" s="3">
         <v>1</v>
@@ -8201,13 +8222,13 @@
         <v>180043</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1281</v>
+        <v>1288</v>
       </c>
       <c r="E42" s="2">
         <v>18</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G42" s="3">
         <v>1</v>
@@ -8227,13 +8248,13 @@
         <v>180044</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>1282</v>
+        <v>1289</v>
       </c>
       <c r="E43" s="2">
         <v>18</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G43" s="3">
         <v>1</v>
@@ -8253,13 +8274,13 @@
         <v>180045</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>1283</v>
+        <v>1290</v>
       </c>
       <c r="E44" s="2">
         <v>18</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G44" s="3">
         <v>1</v>
@@ -8279,13 +8300,13 @@
         <v>180046</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1284</v>
+        <v>1291</v>
       </c>
       <c r="E45" s="2">
         <v>18</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
@@ -8305,13 +8326,13 @@
         <v>180047</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>1285</v>
+        <v>1292</v>
       </c>
       <c r="E46" s="2">
         <v>18</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G46" s="3">
         <v>1</v>
@@ -8331,13 +8352,13 @@
         <v>180048</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1286</v>
+        <v>1293</v>
       </c>
       <c r="E47" s="2">
         <v>18</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G47" s="3">
         <v>1</v>
@@ -8357,13 +8378,13 @@
         <v>180049</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>1287</v>
+        <v>1294</v>
       </c>
       <c r="E48" s="2">
         <v>18</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G48" s="3">
         <v>1</v>
@@ -8383,13 +8404,13 @@
         <v>180050</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>1288</v>
+        <v>1295</v>
       </c>
       <c r="E49" s="2">
         <v>18</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="G49" s="3">
         <v>1</v>
@@ -8548,13 +8569,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1289</v>
+        <v>1296</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -8574,13 +8595,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1291</v>
+        <v>1298</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -8600,13 +8621,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1292</v>
+        <v>1299</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -8626,13 +8647,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1293</v>
+        <v>1300</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -8652,13 +8673,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1294</v>
+        <v>1301</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -8678,13 +8699,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1295</v>
+        <v>1302</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -8706,13 +8727,13 @@
         <v>190007</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1296</v>
+        <v>1303</v>
       </c>
       <c r="E12" s="2">
         <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -8734,13 +8755,13 @@
         <v>190008</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="E13" s="2">
         <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -8762,13 +8783,13 @@
         <v>190009</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1298</v>
+        <v>1305</v>
       </c>
       <c r="E14" s="2">
         <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -8790,13 +8811,13 @@
         <v>190010</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1299</v>
+        <v>1306</v>
       </c>
       <c r="E15" s="2">
         <v>19</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -8818,13 +8839,13 @@
         <v>190011</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1300</v>
+        <v>1307</v>
       </c>
       <c r="E16" s="2">
         <v>19</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -8846,13 +8867,13 @@
         <v>190012</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="E17" s="2">
         <v>19</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -8874,13 +8895,13 @@
         <v>190013</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1302</v>
+        <v>1309</v>
       </c>
       <c r="E18" s="2">
         <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -8902,13 +8923,13 @@
         <v>190014</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1303</v>
+        <v>1310</v>
       </c>
       <c r="E19" s="2">
         <v>19</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -8930,13 +8951,13 @@
         <v>190015</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1304</v>
+        <v>1311</v>
       </c>
       <c r="E20" s="2">
         <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -8958,13 +8979,13 @@
         <v>190016</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1305</v>
+        <v>1312</v>
       </c>
       <c r="E21" s="2">
         <v>19</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -8986,13 +9007,13 @@
         <v>190017</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1306</v>
+        <v>1313</v>
       </c>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -9014,13 +9035,13 @@
         <v>190018</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1307</v>
+        <v>1314</v>
       </c>
       <c r="E23" s="2">
         <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -29530,7 +29551,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M130"/>
+  <dimension ref="C1:M137"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -34027,6 +34048,251 @@
         <v>4015</v>
       </c>
       <c r="M130" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:13">
+      <c r="C131" s="9">
+        <v>50000126</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E131" s="9">
+        <v>5</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G131" s="9">
+        <v>1</v>
+      </c>
+      <c r="H131" s="9">
+        <v>99999</v>
+      </c>
+      <c r="I131" s="9">
+        <v>0</v>
+      </c>
+      <c r="J131" s="9">
+        <v>6</v>
+      </c>
+      <c r="K131" s="9">
+        <v>2150</v>
+      </c>
+      <c r="L131" s="11">
+        <v>4015</v>
+      </c>
+      <c r="M131" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:13">
+      <c r="C132" s="8">
+        <v>50000127</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E132" s="2">
+        <v>5</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G132" s="2">
+        <v>1</v>
+      </c>
+      <c r="H132" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I132" s="2">
+        <v>0</v>
+      </c>
+      <c r="J132" s="2">
+        <v>6</v>
+      </c>
+      <c r="K132" s="2">
+        <v>2200</v>
+      </c>
+      <c r="L132" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M132" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:13">
+      <c r="C133" s="8">
+        <v>50000128</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E133" s="2">
+        <v>5</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G133" s="2">
+        <v>1</v>
+      </c>
+      <c r="H133" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I133" s="2">
+        <v>0</v>
+      </c>
+      <c r="J133" s="2">
+        <v>6</v>
+      </c>
+      <c r="K133" s="2">
+        <v>2250</v>
+      </c>
+      <c r="L133" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M133" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="3:13">
+      <c r="C134" s="8">
+        <v>50000129</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E134" s="2">
+        <v>5</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G134" s="2">
+        <v>1</v>
+      </c>
+      <c r="H134" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I134" s="2">
+        <v>0</v>
+      </c>
+      <c r="J134" s="2">
+        <v>6</v>
+      </c>
+      <c r="K134" s="2">
+        <v>2300</v>
+      </c>
+      <c r="L134" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M134" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="3:13">
+      <c r="C135" s="8">
+        <v>50000130</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E135" s="2">
+        <v>5</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G135" s="2">
+        <v>1</v>
+      </c>
+      <c r="H135" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I135" s="2">
+        <v>0</v>
+      </c>
+      <c r="J135" s="2">
+        <v>6</v>
+      </c>
+      <c r="K135" s="2">
+        <v>2350</v>
+      </c>
+      <c r="L135" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M135" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="3:13">
+      <c r="C136" s="8">
+        <v>50000131</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E136" s="2">
+        <v>5</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G136" s="2">
+        <v>1</v>
+      </c>
+      <c r="H136" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I136" s="2">
+        <v>0</v>
+      </c>
+      <c r="J136" s="2">
+        <v>6</v>
+      </c>
+      <c r="K136" s="2">
+        <v>2400</v>
+      </c>
+      <c r="L136" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M136" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="3:13">
+      <c r="C137" s="8">
+        <v>50000132</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E137" s="2">
+        <v>5</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G137" s="2">
+        <v>1</v>
+      </c>
+      <c r="H137" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I137" s="2">
+        <v>0</v>
+      </c>
+      <c r="J137" s="2">
+        <v>6</v>
+      </c>
+      <c r="K137" s="2">
+        <v>2500</v>
+      </c>
+      <c r="L137" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M137" s="3">
         <v>1</v>
       </c>
     </row>
@@ -34178,13 +34444,13 @@
         <v>60000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -34213,13 +34479,13 @@
         <v>60000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -34248,13 +34514,13 @@
         <v>60000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -34283,13 +34549,13 @@
         <v>60000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -34318,13 +34584,13 @@
         <v>60000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -34353,13 +34619,13 @@
         <v>60000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -34388,13 +34654,13 @@
         <v>60000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -34423,13 +34689,13 @@
         <v>60000008</v>
       </c>
       <c r="D13" s="10" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E13" s="8">
+        <v>5</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>1123</v>
-      </c>
-      <c r="E13" s="8">
-        <v>5</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>1116</v>
       </c>
       <c r="G13" s="8">
         <v>1</v>
@@ -34458,13 +34724,13 @@
         <v>60000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -34493,13 +34759,13 @@
         <v>60000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -34533,13 +34799,13 @@
         <v>60000011</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -34568,13 +34834,13 @@
         <v>60000012</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1127</v>
+        <v>1134</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -34603,13 +34869,13 @@
         <v>60000013</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1128</v>
+        <v>1135</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -34638,13 +34904,13 @@
         <v>60000014</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1129</v>
+        <v>1136</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -34673,13 +34939,13 @@
         <v>60000015</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="E21" s="2">
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -34708,13 +34974,13 @@
         <v>60000016</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1131</v>
+        <v>1138</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -34743,13 +35009,13 @@
         <v>60000017</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -34778,13 +35044,13 @@
         <v>60000018</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
       <c r="E24" s="8">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G24" s="8">
         <v>1</v>
@@ -34813,13 +35079,13 @@
         <v>60000019</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1134</v>
+        <v>1141</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -34848,13 +35114,13 @@
         <v>60000020</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1135</v>
+        <v>1142</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -34883,13 +35149,13 @@
         <v>60000021</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1136</v>
+        <v>1143</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -34918,13 +35184,13 @@
         <v>60000022</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1137</v>
+        <v>1144</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -34953,13 +35219,13 @@
         <v>60000023</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>1138</v>
+        <v>1145</v>
       </c>
       <c r="E29" s="8">
         <v>5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="G29" s="8">
         <v>1</v>
@@ -34998,13 +35264,13 @@
         <v>61000001</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -35033,13 +35299,13 @@
         <v>61000002</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -35068,13 +35334,13 @@
         <v>61000003</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1142</v>
+        <v>1149</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -35103,13 +35369,13 @@
         <v>61000004</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -35138,13 +35404,13 @@
         <v>61000005</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1144</v>
+        <v>1151</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -35173,13 +35439,13 @@
         <v>61000006</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
       <c r="E37" s="2">
         <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -35208,13 +35474,13 @@
         <v>61000007</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1146</v>
+        <v>1153</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -35243,13 +35509,13 @@
         <v>61000008</v>
       </c>
       <c r="D39" s="10" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E39" s="2">
+        <v>5</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>1147</v>
-      </c>
-      <c r="E39" s="2">
-        <v>5</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>1140</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -35283,13 +35549,13 @@
         <v>61000009</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1148</v>
+        <v>1155</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -35318,13 +35584,13 @@
         <v>61000010</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -35353,13 +35619,13 @@
         <v>61000011</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>1150</v>
+        <v>1157</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -35388,13 +35654,13 @@
         <v>61000012</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -35423,13 +35689,13 @@
         <v>61000013</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1152</v>
+        <v>1159</v>
       </c>
       <c r="E45" s="2">
         <v>5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -35458,13 +35724,13 @@
         <v>61000014</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>1153</v>
+        <v>1160</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -35493,13 +35759,13 @@
         <v>61000015</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -35528,13 +35794,13 @@
         <v>61000016</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -35569,13 +35835,13 @@
         <v>61000017</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -35604,13 +35870,13 @@
         <v>61000018</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>1157</v>
+        <v>1164</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -35639,13 +35905,13 @@
         <v>61000019</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>1158</v>
+        <v>1165</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -35674,13 +35940,13 @@
         <v>61000020</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>1159</v>
+        <v>1166</v>
       </c>
       <c r="E53" s="2">
         <v>5</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -35709,13 +35975,13 @@
         <v>61000021</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>1160</v>
+        <v>1167</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -35744,13 +36010,13 @@
         <v>61000022</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -35779,13 +36045,13 @@
         <v>61000023</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>1162</v>
+        <v>1169</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -35814,13 +36080,13 @@
         <v>61000024</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>1163</v>
+        <v>1170</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -35854,13 +36120,13 @@
         <v>61000025</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>1164</v>
+        <v>1171</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -35889,13 +36155,13 @@
         <v>61000026</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1165</v>
+        <v>1172</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -35924,13 +36190,13 @@
         <v>61000027</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>1166</v>
+        <v>1173</v>
       </c>
       <c r="E61" s="2">
         <v>5</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -35959,13 +36225,13 @@
         <v>61000028</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>1167</v>
+        <v>1174</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -35994,13 +36260,13 @@
         <v>61000029</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>1168</v>
+        <v>1175</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -36029,13 +36295,13 @@
         <v>61000030</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>1169</v>
+        <v>1176</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -36064,13 +36330,13 @@
         <v>61000031</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>1170</v>
+        <v>1177</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -36099,13 +36365,13 @@
         <v>61000032</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -36139,13 +36405,13 @@
         <v>61000033</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>1172</v>
+        <v>1179</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -36174,13 +36440,13 @@
         <v>61000034</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>1173</v>
+        <v>1180</v>
       </c>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -36209,13 +36475,13 @@
         <v>61000035</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>1174</v>
+        <v>1181</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -36244,13 +36510,13 @@
         <v>61000036</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>1175</v>
+        <v>1182</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -36279,13 +36545,13 @@
         <v>61000037</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>1176</v>
+        <v>1183</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -36314,13 +36580,13 @@
         <v>61000038</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -36349,13 +36615,13 @@
         <v>61000039</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -36384,13 +36650,13 @@
         <v>61000040</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -36424,13 +36690,13 @@
         <v>61000041</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>1180</v>
+        <v>1187</v>
       </c>
       <c r="E77" s="2">
         <v>5</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -36459,13 +36725,13 @@
         <v>61000042</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>1181</v>
+        <v>1188</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -36494,13 +36760,13 @@
         <v>61000043</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>1182</v>
+        <v>1189</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -36529,13 +36795,13 @@
         <v>61000044</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>1183</v>
+        <v>1190</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -36564,13 +36830,13 @@
         <v>61000045</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>1184</v>
+        <v>1191</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -36599,13 +36865,13 @@
         <v>61000046</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>1185</v>
+        <v>1192</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -36634,13 +36900,13 @@
         <v>61000047</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>1186</v>
+        <v>1193</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -36669,13 +36935,13 @@
         <v>61000048</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>1187</v>
+        <v>1194</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -36709,13 +36975,13 @@
         <v>61000049</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -36744,13 +37010,13 @@
         <v>61000050</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1189</v>
+        <v>1196</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -36779,13 +37045,13 @@
         <v>61000051</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -36814,13 +37080,13 @@
         <v>61000052</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -36849,13 +37115,13 @@
         <v>61000053</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>1192</v>
+        <v>1199</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -36884,13 +37150,13 @@
         <v>61000054</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -36919,13 +37185,13 @@
         <v>61000055</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1194</v>
+        <v>1201</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -36954,13 +37220,13 @@
         <v>61000056</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>1195</v>
+        <v>1202</v>
       </c>
       <c r="E93" s="2">
         <v>5</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -36994,13 +37260,13 @@
         <v>61000057</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>1196</v>
+        <v>1203</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -37029,13 +37295,13 @@
         <v>61000058</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -37064,13 +37330,13 @@
         <v>61000059</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -37099,13 +37365,13 @@
         <v>61000060</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>1199</v>
+        <v>1206</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -37134,13 +37400,13 @@
         <v>61000061</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>1200</v>
+        <v>1207</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -37169,13 +37435,13 @@
         <v>61000062</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1201</v>
+        <v>1208</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -37204,13 +37470,13 @@
         <v>61000063</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="E101" s="2">
         <v>5</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -37239,13 +37505,13 @@
         <v>61000064</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -37279,13 +37545,13 @@
         <v>61000065</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -37314,13 +37580,13 @@
         <v>61000066</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>1205</v>
+        <v>1212</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -37349,13 +37615,13 @@
         <v>61000067</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -37384,13 +37650,13 @@
         <v>61000068</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -37419,13 +37685,13 @@
         <v>61000069</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -37454,13 +37720,13 @@
         <v>61000070</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="E109" s="2">
         <v>5</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -37489,13 +37755,13 @@
         <v>61000071</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="E110" s="2">
         <v>5</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
@@ -37524,13 +37790,13 @@
         <v>61000072</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="E111" s="2">
         <v>5</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -37564,13 +37830,13 @@
         <v>61000073</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="E113" s="2">
         <v>5</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -37599,13 +37865,13 @@
         <v>61000074</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="E114" s="2">
         <v>5</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -37634,13 +37900,13 @@
         <v>61000075</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="E115" s="2">
         <v>5</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
@@ -37669,13 +37935,13 @@
         <v>61000076</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>1215</v>
+        <v>1222</v>
       </c>
       <c r="E116" s="2">
         <v>5</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
@@ -37704,13 +37970,13 @@
         <v>61000077</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="E117" s="2">
         <v>5</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
@@ -37739,13 +38005,13 @@
         <v>61000078</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="E118" s="2">
         <v>5</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G118" s="2">
         <v>1</v>
@@ -37774,13 +38040,13 @@
         <v>61000079</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="E119" s="2">
         <v>5</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G119" s="2">
         <v>1</v>
@@ -37809,13 +38075,13 @@
         <v>61000080</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>1219</v>
+        <v>1226</v>
       </c>
       <c r="E120" s="2">
         <v>5</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G120" s="2">
         <v>1</v>
@@ -37986,13 +38252,13 @@
         <v>70000001</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="E6" s="2">
         <v>32</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -38021,13 +38287,13 @@
         <v>70000002</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1222</v>
+        <v>1229</v>
       </c>
       <c r="E7" s="2">
         <v>32</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -38056,13 +38322,13 @@
         <v>70000003</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="E8" s="2">
         <v>32</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -38091,13 +38357,13 @@
         <v>70000004</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="E9" s="2">
         <v>32</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -38126,13 +38392,13 @@
         <v>70000005</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="E10" s="2">
         <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -38161,13 +38427,13 @@
         <v>70000006</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1226</v>
+        <v>1233</v>
       </c>
       <c r="E11" s="2">
         <v>32</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -38196,13 +38462,13 @@
         <v>70000007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1227</v>
+        <v>1234</v>
       </c>
       <c r="E12" s="2">
         <v>32</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -38231,13 +38497,13 @@
         <v>70000008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1228</v>
+        <v>1235</v>
       </c>
       <c r="E13" s="2">
         <v>32</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -38266,13 +38532,13 @@
         <v>70000011</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1229</v>
+        <v>1236</v>
       </c>
       <c r="E14" s="2">
         <v>32</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -38301,13 +38567,13 @@
         <v>70000012</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1230</v>
+        <v>1237</v>
       </c>
       <c r="E15" s="2">
         <v>32</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -38336,13 +38602,13 @@
         <v>70000013</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1231</v>
+        <v>1238</v>
       </c>
       <c r="E16" s="2">
         <v>32</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -38371,13 +38637,13 @@
         <v>70000014</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1232</v>
+        <v>1239</v>
       </c>
       <c r="E17" s="2">
         <v>32</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -38406,13 +38672,13 @@
         <v>70000015</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="E18" s="2">
         <v>32</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -38441,13 +38707,13 @@
         <v>70000016</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1234</v>
+        <v>1241</v>
       </c>
       <c r="E19" s="2">
         <v>32</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -38476,13 +38742,13 @@
         <v>70000017</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="E20" s="2">
         <v>32</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -38511,13 +38777,13 @@
         <v>70000018</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1236</v>
+        <v>1243</v>
       </c>
       <c r="E21" s="2">
         <v>32</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -38546,13 +38812,13 @@
         <v>70000021</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="E22" s="2">
         <v>32</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -38581,13 +38847,13 @@
         <v>70000022</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1238</v>
+        <v>1245</v>
       </c>
       <c r="E23" s="2">
         <v>32</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -38616,13 +38882,13 @@
         <v>70000023</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1239</v>
+        <v>1246</v>
       </c>
       <c r="E24" s="2">
         <v>32</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -38651,13 +38917,13 @@
         <v>70000024</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="E25" s="2">
         <v>32</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -38686,13 +38952,13 @@
         <v>70000025</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="E26" s="2">
         <v>32</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -38721,13 +38987,13 @@
         <v>70000026</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="E27" s="2">
         <v>32</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -38756,13 +39022,13 @@
         <v>70000027</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="E28" s="2">
         <v>32</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -38791,13 +39057,13 @@
         <v>70000028</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="E29" s="2">
         <v>32</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="6"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -469,7 +469,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2498" uniqueCount="1315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2568" uniqueCount="1350">
   <si>
     <t>_Id</t>
   </si>
@@ -3317,6 +3317,111 @@
   </si>
   <si>
     <t>虚无龙爪</t>
+  </si>
+  <si>
+    <t>鸿蒙鸡爪</t>
+  </si>
+  <si>
+    <t>鸿蒙鹿茸</t>
+  </si>
+  <si>
+    <t>鸿蒙草帽</t>
+  </si>
+  <si>
+    <t>鸿蒙猫爪</t>
+  </si>
+  <si>
+    <t>鸿蒙花朵</t>
+  </si>
+  <si>
+    <t>鸿蒙冰晶</t>
+  </si>
+  <si>
+    <t>鸿蒙蝠翼</t>
+  </si>
+  <si>
+    <t>鸿蒙魂火</t>
+  </si>
+  <si>
+    <t>鸿蒙腐肉</t>
+  </si>
+  <si>
+    <t>鸿蒙蛇胆</t>
+  </si>
+  <si>
+    <t>鸿蒙狼爪</t>
+  </si>
+  <si>
+    <t>鸿蒙虫皮</t>
+  </si>
+  <si>
+    <t>鸿蒙鹰羽</t>
+  </si>
+  <si>
+    <t>鸿蒙虫角</t>
+  </si>
+  <si>
+    <t>鸿蒙蜈膏</t>
+  </si>
+  <si>
+    <t>鸿蒙虫心</t>
+  </si>
+  <si>
+    <t>鸿蒙龙皮</t>
+  </si>
+  <si>
+    <t>鸿蒙猪皮</t>
+  </si>
+  <si>
+    <t>鸿蒙猪心</t>
+  </si>
+  <si>
+    <t>鸿蒙蝎皮</t>
+  </si>
+  <si>
+    <t>鸿蒙宝甲</t>
+  </si>
+  <si>
+    <t>鸿蒙号角</t>
+  </si>
+  <si>
+    <t>鸿蒙雕像</t>
+  </si>
+  <si>
+    <t>鸿蒙神像</t>
+  </si>
+  <si>
+    <t>鸿蒙獠牙</t>
+  </si>
+  <si>
+    <t>鸿蒙树心</t>
+  </si>
+  <si>
+    <t>鸿蒙魔心</t>
+  </si>
+  <si>
+    <t>鸿蒙尸心</t>
+  </si>
+  <si>
+    <t>鸿蒙法杖</t>
+  </si>
+  <si>
+    <t>鸿蒙权杖</t>
+  </si>
+  <si>
+    <t>鸿蒙战锤</t>
+  </si>
+  <si>
+    <t>鸿蒙血核</t>
+  </si>
+  <si>
+    <t>鸿蒙魔核</t>
+  </si>
+  <si>
+    <t>鸿蒙龙甲</t>
+  </si>
+  <si>
+    <t>鸿蒙龙爪</t>
   </si>
   <si>
     <t>二阶武器升阶石</t>
@@ -7259,13 +7364,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1252</v>
+        <v>1287</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -7285,13 +7390,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1254</v>
+        <v>1289</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7311,13 +7416,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1255</v>
+        <v>1290</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7337,13 +7442,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1256</v>
+        <v>1291</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7363,13 +7468,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1257</v>
+        <v>1292</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -7389,13 +7494,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1258</v>
+        <v>1293</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -7417,13 +7522,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1259</v>
+        <v>1294</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -7445,13 +7550,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1260</v>
+        <v>1295</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -7473,13 +7578,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -7501,13 +7606,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1262</v>
+        <v>1297</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -7529,13 +7634,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1263</v>
+        <v>1298</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -7557,13 +7662,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1264</v>
+        <v>1299</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -7585,13 +7690,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1265</v>
+        <v>1300</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -7613,13 +7718,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1266</v>
+        <v>1301</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -7641,13 +7746,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1267</v>
+        <v>1302</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -7669,13 +7774,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1268</v>
+        <v>1303</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -7697,13 +7802,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1269</v>
+        <v>1304</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -7725,13 +7830,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1270</v>
+        <v>1305</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -7753,13 +7858,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1271</v>
+        <v>1306</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -7781,13 +7886,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -7809,13 +7914,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -7837,13 +7942,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1274</v>
+        <v>1309</v>
       </c>
       <c r="E27" s="2">
         <v>18</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -7870,13 +7975,13 @@
         <v>180030</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1275</v>
+        <v>1310</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -7898,13 +8003,13 @@
         <v>180031</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1276</v>
+        <v>1311</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -7924,13 +8029,13 @@
         <v>180032</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1277</v>
+        <v>1312</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -7950,13 +8055,13 @@
         <v>180033</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1278</v>
+        <v>1313</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -7976,13 +8081,13 @@
         <v>180034</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1279</v>
+        <v>1314</v>
       </c>
       <c r="E33" s="2">
         <v>18</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -8004,13 +8109,13 @@
         <v>180035</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1280</v>
+        <v>1315</v>
       </c>
       <c r="E34" s="2">
         <v>18</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -8032,13 +8137,13 @@
         <v>180036</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1281</v>
+        <v>1316</v>
       </c>
       <c r="E35" s="2">
         <v>18</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -8060,13 +8165,13 @@
         <v>180037</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1282</v>
+        <v>1317</v>
       </c>
       <c r="E36" s="2">
         <v>18</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -8088,13 +8193,13 @@
         <v>180038</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>1283</v>
+        <v>1318</v>
       </c>
       <c r="E37" s="2">
         <v>18</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G37" s="3">
         <v>1</v>
@@ -8116,13 +8221,13 @@
         <v>180039</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1284</v>
+        <v>1319</v>
       </c>
       <c r="E38" s="2">
         <v>18</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -8144,13 +8249,13 @@
         <v>180040</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>1285</v>
+        <v>1320</v>
       </c>
       <c r="E39" s="2">
         <v>18</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G39" s="3">
         <v>1</v>
@@ -8170,13 +8275,13 @@
         <v>180041</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>1286</v>
+        <v>1321</v>
       </c>
       <c r="E40" s="2">
         <v>18</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G40" s="3">
         <v>1</v>
@@ -8196,13 +8301,13 @@
         <v>180042</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1287</v>
+        <v>1322</v>
       </c>
       <c r="E41" s="2">
         <v>18</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G41" s="3">
         <v>1</v>
@@ -8222,13 +8327,13 @@
         <v>180043</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1288</v>
+        <v>1323</v>
       </c>
       <c r="E42" s="2">
         <v>18</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G42" s="3">
         <v>1</v>
@@ -8248,13 +8353,13 @@
         <v>180044</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>1289</v>
+        <v>1324</v>
       </c>
       <c r="E43" s="2">
         <v>18</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G43" s="3">
         <v>1</v>
@@ -8274,13 +8379,13 @@
         <v>180045</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>1290</v>
+        <v>1325</v>
       </c>
       <c r="E44" s="2">
         <v>18</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G44" s="3">
         <v>1</v>
@@ -8300,13 +8405,13 @@
         <v>180046</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1291</v>
+        <v>1326</v>
       </c>
       <c r="E45" s="2">
         <v>18</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
@@ -8326,13 +8431,13 @@
         <v>180047</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>1292</v>
+        <v>1327</v>
       </c>
       <c r="E46" s="2">
         <v>18</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G46" s="3">
         <v>1</v>
@@ -8352,13 +8457,13 @@
         <v>180048</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1293</v>
+        <v>1328</v>
       </c>
       <c r="E47" s="2">
         <v>18</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G47" s="3">
         <v>1</v>
@@ -8378,13 +8483,13 @@
         <v>180049</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>1294</v>
+        <v>1329</v>
       </c>
       <c r="E48" s="2">
         <v>18</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G48" s="3">
         <v>1</v>
@@ -8404,13 +8509,13 @@
         <v>180050</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>1295</v>
+        <v>1330</v>
       </c>
       <c r="E49" s="2">
         <v>18</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>1253</v>
+        <v>1288</v>
       </c>
       <c r="G49" s="3">
         <v>1</v>
@@ -8569,13 +8674,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1296</v>
+        <v>1331</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -8595,13 +8700,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1298</v>
+        <v>1333</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -8621,13 +8726,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1299</v>
+        <v>1334</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -8647,13 +8752,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1300</v>
+        <v>1335</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -8673,13 +8778,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1301</v>
+        <v>1336</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -8699,13 +8804,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1302</v>
+        <v>1337</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -8727,13 +8832,13 @@
         <v>190007</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1303</v>
+        <v>1338</v>
       </c>
       <c r="E12" s="2">
         <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -8755,13 +8860,13 @@
         <v>190008</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1304</v>
+        <v>1339</v>
       </c>
       <c r="E13" s="2">
         <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -8783,13 +8888,13 @@
         <v>190009</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1305</v>
+        <v>1340</v>
       </c>
       <c r="E14" s="2">
         <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -8811,13 +8916,13 @@
         <v>190010</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1306</v>
+        <v>1341</v>
       </c>
       <c r="E15" s="2">
         <v>19</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -8839,13 +8944,13 @@
         <v>190011</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1307</v>
+        <v>1342</v>
       </c>
       <c r="E16" s="2">
         <v>19</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -8867,13 +8972,13 @@
         <v>190012</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1308</v>
+        <v>1343</v>
       </c>
       <c r="E17" s="2">
         <v>19</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -8895,13 +9000,13 @@
         <v>190013</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1309</v>
+        <v>1344</v>
       </c>
       <c r="E18" s="2">
         <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -8923,13 +9028,13 @@
         <v>190014</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1310</v>
+        <v>1345</v>
       </c>
       <c r="E19" s="2">
         <v>19</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -8951,13 +9056,13 @@
         <v>190015</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1311</v>
+        <v>1346</v>
       </c>
       <c r="E20" s="2">
         <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -8979,13 +9084,13 @@
         <v>190016</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1312</v>
+        <v>1347</v>
       </c>
       <c r="E21" s="2">
         <v>19</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -9007,13 +9112,13 @@
         <v>190017</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1313</v>
+        <v>1348</v>
       </c>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -9035,13 +9140,13 @@
         <v>190018</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1314</v>
+        <v>1349</v>
       </c>
       <c r="E23" s="2">
         <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -22548,7 +22653,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M200"/>
+  <dimension ref="C1:M235"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -29343,7 +29448,7 @@
         <v>6</v>
       </c>
       <c r="K195" s="14">
-        <f t="shared" ref="K195:K200" si="1">K190+50</f>
+        <f t="shared" ref="K195:K235" si="1">K190+50</f>
         <v>2400</v>
       </c>
       <c r="L195" s="3">
@@ -29530,6 +29635,1266 @@
         <v>4018</v>
       </c>
       <c r="M200" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" spans="3:13">
+      <c r="C201" s="3">
+        <v>40000245</v>
+      </c>
+      <c r="D201" s="13" t="s">
+        <v>884</v>
+      </c>
+      <c r="E201" s="2">
+        <v>14</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G201" s="2">
+        <v>1</v>
+      </c>
+      <c r="H201" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I201" s="2">
+        <v>0</v>
+      </c>
+      <c r="J201" s="2">
+        <v>6</v>
+      </c>
+      <c r="K201" s="14">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="L201" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M201" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" spans="3:13">
+      <c r="C202" s="3">
+        <v>40000246</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="E202" s="2">
+        <v>14</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G202" s="2">
+        <v>1</v>
+      </c>
+      <c r="H202" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I202" s="2">
+        <v>0</v>
+      </c>
+      <c r="J202" s="2">
+        <v>6</v>
+      </c>
+      <c r="K202" s="14">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="L202" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M202" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" spans="3:13">
+      <c r="C203" s="3">
+        <v>40000247</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="E203" s="2">
+        <v>14</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G203" s="2">
+        <v>1</v>
+      </c>
+      <c r="H203" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I203" s="2">
+        <v>0</v>
+      </c>
+      <c r="J203" s="2">
+        <v>6</v>
+      </c>
+      <c r="K203" s="14">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="L203" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M203" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" spans="3:13">
+      <c r="C204" s="3">
+        <v>40000248</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="E204" s="2">
+        <v>14</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G204" s="2">
+        <v>1</v>
+      </c>
+      <c r="H204" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I204" s="2">
+        <v>0</v>
+      </c>
+      <c r="J204" s="2">
+        <v>6</v>
+      </c>
+      <c r="K204" s="14">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="L204" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M204" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="3:13">
+      <c r="C205" s="3">
+        <v>40000249</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="E205" s="2">
+        <v>14</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G205" s="2">
+        <v>1</v>
+      </c>
+      <c r="H205" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I205" s="2">
+        <v>0</v>
+      </c>
+      <c r="J205" s="2">
+        <v>6</v>
+      </c>
+      <c r="K205" s="14">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="L205" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M205" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" spans="3:13">
+      <c r="C206" s="3">
+        <v>40000250</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="E206" s="2">
+        <v>14</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G206" s="2">
+        <v>1</v>
+      </c>
+      <c r="H206" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I206" s="2">
+        <v>0</v>
+      </c>
+      <c r="J206" s="2">
+        <v>6</v>
+      </c>
+      <c r="K206" s="14">
+        <f t="shared" si="1"/>
+        <v>2550</v>
+      </c>
+      <c r="L206" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M206" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" spans="3:13">
+      <c r="C207" s="3">
+        <v>40000251</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="E207" s="2">
+        <v>14</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G207" s="2">
+        <v>1</v>
+      </c>
+      <c r="H207" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I207" s="2">
+        <v>0</v>
+      </c>
+      <c r="J207" s="2">
+        <v>6</v>
+      </c>
+      <c r="K207" s="14">
+        <f t="shared" si="1"/>
+        <v>2550</v>
+      </c>
+      <c r="L207" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M207" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" spans="3:13">
+      <c r="C208" s="3">
+        <v>40000252</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="E208" s="2">
+        <v>14</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G208" s="2">
+        <v>1</v>
+      </c>
+      <c r="H208" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I208" s="2">
+        <v>0</v>
+      </c>
+      <c r="J208" s="2">
+        <v>6</v>
+      </c>
+      <c r="K208" s="14">
+        <f t="shared" si="1"/>
+        <v>2550</v>
+      </c>
+      <c r="L208" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M208" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" spans="3:13">
+      <c r="C209" s="3">
+        <v>40000253</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="E209" s="2">
+        <v>14</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G209" s="2">
+        <v>1</v>
+      </c>
+      <c r="H209" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I209" s="2">
+        <v>0</v>
+      </c>
+      <c r="J209" s="2">
+        <v>6</v>
+      </c>
+      <c r="K209" s="14">
+        <f t="shared" si="1"/>
+        <v>2550</v>
+      </c>
+      <c r="L209" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M209" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" spans="3:13">
+      <c r="C210" s="3">
+        <v>40000254</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="E210" s="2">
+        <v>14</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G210" s="2">
+        <v>1</v>
+      </c>
+      <c r="H210" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I210" s="2">
+        <v>0</v>
+      </c>
+      <c r="J210" s="2">
+        <v>6</v>
+      </c>
+      <c r="K210" s="14">
+        <f t="shared" si="1"/>
+        <v>2550</v>
+      </c>
+      <c r="L210" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M210" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" spans="3:13">
+      <c r="C211" s="3">
+        <v>40000255</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="E211" s="2">
+        <v>14</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G211" s="2">
+        <v>1</v>
+      </c>
+      <c r="H211" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I211" s="2">
+        <v>0</v>
+      </c>
+      <c r="J211" s="2">
+        <v>6</v>
+      </c>
+      <c r="K211" s="14">
+        <f t="shared" si="1"/>
+        <v>2600</v>
+      </c>
+      <c r="L211" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M211" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" customHeight="1" spans="3:13">
+      <c r="C212" s="3">
+        <v>40000256</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="E212" s="2">
+        <v>14</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G212" s="2">
+        <v>1</v>
+      </c>
+      <c r="H212" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I212" s="2">
+        <v>0</v>
+      </c>
+      <c r="J212" s="2">
+        <v>6</v>
+      </c>
+      <c r="K212" s="14">
+        <f t="shared" si="1"/>
+        <v>2600</v>
+      </c>
+      <c r="L212" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M212" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" customHeight="1" spans="3:13">
+      <c r="C213" s="3">
+        <v>40000257</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="E213" s="2">
+        <v>14</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G213" s="2">
+        <v>1</v>
+      </c>
+      <c r="H213" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I213" s="2">
+        <v>0</v>
+      </c>
+      <c r="J213" s="2">
+        <v>6</v>
+      </c>
+      <c r="K213" s="14">
+        <f t="shared" si="1"/>
+        <v>2600</v>
+      </c>
+      <c r="L213" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M213" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" spans="3:13">
+      <c r="C214" s="3">
+        <v>40000258</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="E214" s="2">
+        <v>14</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G214" s="2">
+        <v>1</v>
+      </c>
+      <c r="H214" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I214" s="2">
+        <v>0</v>
+      </c>
+      <c r="J214" s="2">
+        <v>6</v>
+      </c>
+      <c r="K214" s="14">
+        <f t="shared" si="1"/>
+        <v>2600</v>
+      </c>
+      <c r="L214" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M214" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" customHeight="1" spans="3:13">
+      <c r="C215" s="3">
+        <v>40000259</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="E215" s="2">
+        <v>14</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G215" s="2">
+        <v>1</v>
+      </c>
+      <c r="H215" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I215" s="2">
+        <v>0</v>
+      </c>
+      <c r="J215" s="2">
+        <v>6</v>
+      </c>
+      <c r="K215" s="14">
+        <f t="shared" si="1"/>
+        <v>2600</v>
+      </c>
+      <c r="L215" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M215" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" spans="3:13">
+      <c r="C216" s="3">
+        <v>40000260</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="E216" s="2">
+        <v>14</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G216" s="2">
+        <v>1</v>
+      </c>
+      <c r="H216" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I216" s="2">
+        <v>0</v>
+      </c>
+      <c r="J216" s="2">
+        <v>6</v>
+      </c>
+      <c r="K216" s="14">
+        <f t="shared" si="1"/>
+        <v>2650</v>
+      </c>
+      <c r="L216" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M216" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" spans="3:13">
+      <c r="C217" s="3">
+        <v>40000261</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="E217" s="2">
+        <v>14</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G217" s="2">
+        <v>1</v>
+      </c>
+      <c r="H217" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I217" s="2">
+        <v>0</v>
+      </c>
+      <c r="J217" s="2">
+        <v>6</v>
+      </c>
+      <c r="K217" s="14">
+        <f t="shared" si="1"/>
+        <v>2650</v>
+      </c>
+      <c r="L217" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M217" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" spans="3:13">
+      <c r="C218" s="3">
+        <v>40000262</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="E218" s="2">
+        <v>14</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G218" s="2">
+        <v>1</v>
+      </c>
+      <c r="H218" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I218" s="2">
+        <v>0</v>
+      </c>
+      <c r="J218" s="2">
+        <v>6</v>
+      </c>
+      <c r="K218" s="14">
+        <f t="shared" si="1"/>
+        <v>2650</v>
+      </c>
+      <c r="L218" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M218" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" spans="3:13">
+      <c r="C219" s="3">
+        <v>40000263</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="E219" s="2">
+        <v>14</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G219" s="2">
+        <v>1</v>
+      </c>
+      <c r="H219" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I219" s="2">
+        <v>0</v>
+      </c>
+      <c r="J219" s="2">
+        <v>6</v>
+      </c>
+      <c r="K219" s="14">
+        <f t="shared" si="1"/>
+        <v>2650</v>
+      </c>
+      <c r="L219" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M219" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" spans="3:13">
+      <c r="C220" s="3">
+        <v>40000264</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="E220" s="2">
+        <v>14</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G220" s="2">
+        <v>1</v>
+      </c>
+      <c r="H220" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I220" s="2">
+        <v>0</v>
+      </c>
+      <c r="J220" s="2">
+        <v>6</v>
+      </c>
+      <c r="K220" s="14">
+        <f t="shared" si="1"/>
+        <v>2650</v>
+      </c>
+      <c r="L220" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M220" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" spans="3:13">
+      <c r="C221" s="3">
+        <v>40000265</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="E221" s="2">
+        <v>14</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G221" s="2">
+        <v>1</v>
+      </c>
+      <c r="H221" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I221" s="2">
+        <v>0</v>
+      </c>
+      <c r="J221" s="2">
+        <v>6</v>
+      </c>
+      <c r="K221" s="14">
+        <f t="shared" si="1"/>
+        <v>2700</v>
+      </c>
+      <c r="L221" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M221" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" spans="3:13">
+      <c r="C222" s="3">
+        <v>40000266</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="E222" s="2">
+        <v>14</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G222" s="2">
+        <v>1</v>
+      </c>
+      <c r="H222" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I222" s="2">
+        <v>0</v>
+      </c>
+      <c r="J222" s="2">
+        <v>6</v>
+      </c>
+      <c r="K222" s="14">
+        <f t="shared" si="1"/>
+        <v>2700</v>
+      </c>
+      <c r="L222" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M222" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" spans="3:13">
+      <c r="C223" s="3">
+        <v>40000267</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="E223" s="2">
+        <v>14</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G223" s="2">
+        <v>1</v>
+      </c>
+      <c r="H223" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I223" s="2">
+        <v>0</v>
+      </c>
+      <c r="J223" s="2">
+        <v>6</v>
+      </c>
+      <c r="K223" s="14">
+        <f t="shared" si="1"/>
+        <v>2700</v>
+      </c>
+      <c r="L223" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M223" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" spans="3:13">
+      <c r="C224" s="3">
+        <v>40000268</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="E224" s="2">
+        <v>14</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G224" s="2">
+        <v>1</v>
+      </c>
+      <c r="H224" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I224" s="2">
+        <v>0</v>
+      </c>
+      <c r="J224" s="2">
+        <v>6</v>
+      </c>
+      <c r="K224" s="14">
+        <f t="shared" si="1"/>
+        <v>2700</v>
+      </c>
+      <c r="L224" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M224" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" spans="3:13">
+      <c r="C225" s="3">
+        <v>40000269</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="E225" s="2">
+        <v>14</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G225" s="2">
+        <v>1</v>
+      </c>
+      <c r="H225" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I225" s="2">
+        <v>0</v>
+      </c>
+      <c r="J225" s="2">
+        <v>6</v>
+      </c>
+      <c r="K225" s="14">
+        <f t="shared" si="1"/>
+        <v>2700</v>
+      </c>
+      <c r="L225" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M225" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" spans="3:13">
+      <c r="C226" s="3">
+        <v>40000270</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="E226" s="2">
+        <v>14</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G226" s="2">
+        <v>1</v>
+      </c>
+      <c r="H226" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I226" s="2">
+        <v>0</v>
+      </c>
+      <c r="J226" s="2">
+        <v>6</v>
+      </c>
+      <c r="K226" s="14">
+        <f t="shared" si="1"/>
+        <v>2750</v>
+      </c>
+      <c r="L226" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M226" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" spans="3:13">
+      <c r="C227" s="3">
+        <v>40000271</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="E227" s="2">
+        <v>14</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G227" s="2">
+        <v>1</v>
+      </c>
+      <c r="H227" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I227" s="2">
+        <v>0</v>
+      </c>
+      <c r="J227" s="2">
+        <v>6</v>
+      </c>
+      <c r="K227" s="14">
+        <f t="shared" si="1"/>
+        <v>2750</v>
+      </c>
+      <c r="L227" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M227" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" spans="3:13">
+      <c r="C228" s="3">
+        <v>40000272</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="E228" s="2">
+        <v>14</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G228" s="2">
+        <v>1</v>
+      </c>
+      <c r="H228" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I228" s="2">
+        <v>0</v>
+      </c>
+      <c r="J228" s="2">
+        <v>6</v>
+      </c>
+      <c r="K228" s="14">
+        <f t="shared" si="1"/>
+        <v>2750</v>
+      </c>
+      <c r="L228" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M228" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" spans="3:13">
+      <c r="C229" s="3">
+        <v>40000273</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="E229" s="2">
+        <v>14</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G229" s="2">
+        <v>1</v>
+      </c>
+      <c r="H229" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I229" s="2">
+        <v>0</v>
+      </c>
+      <c r="J229" s="2">
+        <v>6</v>
+      </c>
+      <c r="K229" s="14">
+        <f t="shared" si="1"/>
+        <v>2750</v>
+      </c>
+      <c r="L229" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M229" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" customHeight="1" spans="3:13">
+      <c r="C230" s="3">
+        <v>40000274</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="E230" s="2">
+        <v>14</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G230" s="2">
+        <v>1</v>
+      </c>
+      <c r="H230" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I230" s="2">
+        <v>0</v>
+      </c>
+      <c r="J230" s="2">
+        <v>6</v>
+      </c>
+      <c r="K230" s="14">
+        <f t="shared" si="1"/>
+        <v>2750</v>
+      </c>
+      <c r="L230" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M230" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" spans="3:13">
+      <c r="C231" s="3">
+        <v>40000275</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="E231" s="2">
+        <v>14</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G231" s="2">
+        <v>1</v>
+      </c>
+      <c r="H231" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I231" s="2">
+        <v>0</v>
+      </c>
+      <c r="J231" s="2">
+        <v>6</v>
+      </c>
+      <c r="K231" s="14">
+        <f t="shared" si="1"/>
+        <v>2800</v>
+      </c>
+      <c r="L231" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M231" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" spans="3:13">
+      <c r="C232" s="3">
+        <v>40000276</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="E232" s="2">
+        <v>14</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G232" s="2">
+        <v>1</v>
+      </c>
+      <c r="H232" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I232" s="2">
+        <v>0</v>
+      </c>
+      <c r="J232" s="2">
+        <v>6</v>
+      </c>
+      <c r="K232" s="14">
+        <f t="shared" si="1"/>
+        <v>2800</v>
+      </c>
+      <c r="L232" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M232" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" spans="3:13">
+      <c r="C233" s="3">
+        <v>40000277</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="E233" s="2">
+        <v>14</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G233" s="2">
+        <v>1</v>
+      </c>
+      <c r="H233" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I233" s="2">
+        <v>0</v>
+      </c>
+      <c r="J233" s="2">
+        <v>6</v>
+      </c>
+      <c r="K233" s="14">
+        <f t="shared" si="1"/>
+        <v>2800</v>
+      </c>
+      <c r="L233" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M233" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" spans="3:13">
+      <c r="C234" s="3">
+        <v>40000278</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="E234" s="2">
+        <v>14</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G234" s="2">
+        <v>1</v>
+      </c>
+      <c r="H234" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I234" s="2">
+        <v>0</v>
+      </c>
+      <c r="J234" s="2">
+        <v>6</v>
+      </c>
+      <c r="K234" s="14">
+        <f t="shared" si="1"/>
+        <v>2800</v>
+      </c>
+      <c r="L234" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M234" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" spans="3:13">
+      <c r="C235" s="3">
+        <v>40000279</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="E235" s="2">
+        <v>14</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G235" s="2">
+        <v>1</v>
+      </c>
+      <c r="H235" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I235" s="2">
+        <v>0</v>
+      </c>
+      <c r="J235" s="2">
+        <v>6</v>
+      </c>
+      <c r="K235" s="14">
+        <f t="shared" si="1"/>
+        <v>2800</v>
+      </c>
+      <c r="L235" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M235" s="3">
         <v>1</v>
       </c>
     </row>
@@ -29681,13 +31046,13 @@
         <v>50000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>884</v>
+        <v>919</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>885</v>
+        <v>920</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -29716,13 +31081,13 @@
         <v>50000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>886</v>
+        <v>921</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>887</v>
+        <v>922</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -29751,13 +31116,13 @@
         <v>50000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>888</v>
+        <v>923</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -29786,13 +31151,13 @@
         <v>50000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>890</v>
+        <v>925</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>891</v>
+        <v>926</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -29821,13 +31186,13 @@
         <v>50000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>892</v>
+        <v>927</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>893</v>
+        <v>928</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -29856,13 +31221,13 @@
         <v>50000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>894</v>
+        <v>929</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>895</v>
+        <v>930</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -29891,13 +31256,13 @@
         <v>50000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>896</v>
+        <v>931</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>897</v>
+        <v>932</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -29926,13 +31291,13 @@
         <v>50000008</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>898</v>
+        <v>933</v>
       </c>
       <c r="E13" s="9">
         <v>5</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>899</v>
+        <v>934</v>
       </c>
       <c r="G13" s="9">
         <v>1</v>
@@ -29961,13 +31326,13 @@
         <v>50000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>900</v>
+        <v>935</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>901</v>
+        <v>936</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -29996,13 +31361,13 @@
         <v>50000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>902</v>
+        <v>937</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>903</v>
+        <v>938</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -30031,13 +31396,13 @@
         <v>50000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>904</v>
+        <v>939</v>
       </c>
       <c r="E16" s="2">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>905</v>
+        <v>940</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -30066,13 +31431,13 @@
         <v>50000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>906</v>
+        <v>941</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>907</v>
+        <v>942</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -30101,13 +31466,13 @@
         <v>50000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>908</v>
+        <v>943</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>909</v>
+        <v>944</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -30136,13 +31501,13 @@
         <v>50000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>910</v>
+        <v>945</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>911</v>
+        <v>946</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -30171,13 +31536,13 @@
         <v>50000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>912</v>
+        <v>947</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>913</v>
+        <v>948</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -30206,13 +31571,13 @@
         <v>50000016</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>914</v>
+        <v>949</v>
       </c>
       <c r="E21" s="9">
         <v>5</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>915</v>
+        <v>950</v>
       </c>
       <c r="G21" s="9">
         <v>1</v>
@@ -30241,13 +31606,13 @@
         <v>50000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>916</v>
+        <v>951</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>917</v>
+        <v>952</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -30276,13 +31641,13 @@
         <v>50000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>918</v>
+        <v>953</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>919</v>
+        <v>954</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -30311,13 +31676,13 @@
         <v>50000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>920</v>
+        <v>955</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>921</v>
+        <v>956</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -30346,13 +31711,13 @@
         <v>50000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>922</v>
+        <v>957</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>923</v>
+        <v>958</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -30381,13 +31746,13 @@
         <v>50000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>924</v>
+        <v>959</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>925</v>
+        <v>960</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -30416,13 +31781,13 @@
         <v>50000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>926</v>
+        <v>961</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>927</v>
+        <v>962</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -30451,13 +31816,13 @@
         <v>50000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>928</v>
+        <v>963</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>929</v>
+        <v>964</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -30486,13 +31851,13 @@
         <v>50000024</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>930</v>
+        <v>965</v>
       </c>
       <c r="E29" s="9">
         <v>5</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>931</v>
+        <v>966</v>
       </c>
       <c r="G29" s="9">
         <v>1</v>
@@ -30521,13 +31886,13 @@
         <v>50000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>932</v>
+        <v>967</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>933</v>
+        <v>968</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -30556,13 +31921,13 @@
         <v>50000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>934</v>
+        <v>969</v>
       </c>
       <c r="E31" s="2">
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>935</v>
+        <v>970</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -30591,13 +31956,13 @@
         <v>50000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>936</v>
+        <v>971</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>937</v>
+        <v>972</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -30626,13 +31991,13 @@
         <v>50000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>938</v>
+        <v>973</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>939</v>
+        <v>974</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -30661,13 +32026,13 @@
         <v>50000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>940</v>
+        <v>975</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>941</v>
+        <v>976</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -30696,13 +32061,13 @@
         <v>50000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>942</v>
+        <v>977</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>943</v>
+        <v>978</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -30731,13 +32096,13 @@
         <v>50000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>944</v>
+        <v>979</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>945</v>
+        <v>980</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -30766,13 +32131,13 @@
         <v>50000032</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>946</v>
+        <v>981</v>
       </c>
       <c r="E37" s="9">
         <v>5</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>947</v>
+        <v>982</v>
       </c>
       <c r="G37" s="9">
         <v>1</v>
@@ -30801,13 +32166,13 @@
         <v>50000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>948</v>
+        <v>983</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>949</v>
+        <v>984</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -30836,13 +32201,13 @@
         <v>50000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>950</v>
+        <v>985</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>951</v>
+        <v>986</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -30871,13 +32236,13 @@
         <v>50000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>952</v>
+        <v>987</v>
       </c>
       <c r="E40" s="2">
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>953</v>
+        <v>988</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -30906,13 +32271,13 @@
         <v>50000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>954</v>
+        <v>989</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>955</v>
+        <v>990</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -30941,13 +32306,13 @@
         <v>50000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>956</v>
+        <v>991</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>957</v>
+        <v>992</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -30976,13 +32341,13 @@
         <v>50000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>958</v>
+        <v>993</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>959</v>
+        <v>994</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -31011,13 +32376,13 @@
         <v>50000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>960</v>
+        <v>995</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>961</v>
+        <v>996</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -31046,13 +32411,13 @@
         <v>50000040</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>962</v>
+        <v>997</v>
       </c>
       <c r="E45" s="9">
         <v>5</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>963</v>
+        <v>998</v>
       </c>
       <c r="G45" s="9">
         <v>1</v>
@@ -31081,13 +32446,13 @@
         <v>50000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>964</v>
+        <v>999</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>965</v>
+        <v>1000</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -31116,13 +32481,13 @@
         <v>50000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>966</v>
+        <v>1001</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -31151,13 +32516,13 @@
         <v>50000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>968</v>
+        <v>1003</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>969</v>
+        <v>1004</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -31186,13 +32551,13 @@
         <v>50000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>970</v>
+        <v>1005</v>
       </c>
       <c r="E49" s="2">
         <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>971</v>
+        <v>1006</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -31221,13 +32586,13 @@
         <v>50000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>972</v>
+        <v>1007</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>973</v>
+        <v>1008</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -31256,13 +32621,13 @@
         <v>50000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>975</v>
+        <v>1010</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -31291,13 +32656,13 @@
         <v>50000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>976</v>
+        <v>1011</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>977</v>
+        <v>1012</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -31326,13 +32691,13 @@
         <v>50000048</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>978</v>
+        <v>1013</v>
       </c>
       <c r="E53" s="9">
         <v>5</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="G53" s="9">
         <v>1</v>
@@ -31361,13 +32726,13 @@
         <v>50000049</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>980</v>
+        <v>1015</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>981</v>
+        <v>1016</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -31396,13 +32761,13 @@
         <v>50000050</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>982</v>
+        <v>1017</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>983</v>
+        <v>1018</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -31431,13 +32796,13 @@
         <v>50000051</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>984</v>
+        <v>1019</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>985</v>
+        <v>1020</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -31466,13 +32831,13 @@
         <v>50000052</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>986</v>
+        <v>1021</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>987</v>
+        <v>1022</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -31501,13 +32866,13 @@
         <v>50000053</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>988</v>
+        <v>1023</v>
       </c>
       <c r="E58" s="2">
         <v>5</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>989</v>
+        <v>1024</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -31536,13 +32901,13 @@
         <v>50000054</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>990</v>
+        <v>1025</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>991</v>
+        <v>1026</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -31571,13 +32936,13 @@
         <v>50000055</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>992</v>
+        <v>1027</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>993</v>
+        <v>1028</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -31606,13 +32971,13 @@
         <v>50000056</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>994</v>
+        <v>1029</v>
       </c>
       <c r="E61" s="9">
         <v>5</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>995</v>
+        <v>1030</v>
       </c>
       <c r="G61" s="9">
         <v>1</v>
@@ -31641,13 +33006,13 @@
         <v>50000057</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>996</v>
+        <v>1031</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>997</v>
+        <v>1032</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -31676,13 +33041,13 @@
         <v>50000058</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>998</v>
+        <v>1033</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>999</v>
+        <v>1034</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -31711,13 +33076,13 @@
         <v>50000059</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>1000</v>
+        <v>1035</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>1001</v>
+        <v>1036</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -31746,13 +33111,13 @@
         <v>50000060</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>1002</v>
+        <v>1037</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>1003</v>
+        <v>1038</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -31781,13 +33146,13 @@
         <v>50000061</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>1004</v>
+        <v>1039</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>1005</v>
+        <v>1040</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -31816,13 +33181,13 @@
         <v>50000062</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>1006</v>
+        <v>1041</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>1007</v>
+        <v>1042</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -31851,13 +33216,13 @@
         <v>50000063</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>1008</v>
+        <v>1043</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>1009</v>
+        <v>1044</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -31886,13 +33251,13 @@
         <v>50000064</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>1010</v>
+        <v>1045</v>
       </c>
       <c r="E69" s="9">
         <v>5</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>1011</v>
+        <v>1046</v>
       </c>
       <c r="G69" s="9">
         <v>1</v>
@@ -31921,13 +33286,13 @@
         <v>50000065</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>1012</v>
+        <v>1047</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>1013</v>
+        <v>1048</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -31956,13 +33321,13 @@
         <v>50000066</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>1014</v>
+        <v>1049</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>1015</v>
+        <v>1050</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -31991,13 +33356,13 @@
         <v>50000067</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>1016</v>
+        <v>1051</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>1017</v>
+        <v>1052</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -32026,13 +33391,13 @@
         <v>50000068</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>1018</v>
+        <v>1053</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>1019</v>
+        <v>1054</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -32061,13 +33426,13 @@
         <v>50000069</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>1020</v>
+        <v>1055</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>1021</v>
+        <v>1056</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -32096,13 +33461,13 @@
         <v>50000070</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>1022</v>
+        <v>1057</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>1023</v>
+        <v>1058</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -32131,13 +33496,13 @@
         <v>50000071</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>1024</v>
+        <v>1059</v>
       </c>
       <c r="E76" s="2">
         <v>5</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>1025</v>
+        <v>1060</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -32166,13 +33531,13 @@
         <v>50000072</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>1026</v>
+        <v>1061</v>
       </c>
       <c r="E77" s="9">
         <v>5</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>1027</v>
+        <v>1062</v>
       </c>
       <c r="G77" s="9">
         <v>1</v>
@@ -32201,13 +33566,13 @@
         <v>50000073</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>1028</v>
+        <v>1063</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>1029</v>
+        <v>1064</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -32236,13 +33601,13 @@
         <v>50000074</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>1030</v>
+        <v>1065</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>1031</v>
+        <v>1066</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -32271,13 +33636,13 @@
         <v>50000075</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>1032</v>
+        <v>1067</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>1033</v>
+        <v>1068</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -32306,13 +33671,13 @@
         <v>50000076</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>1034</v>
+        <v>1069</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>1035</v>
+        <v>1070</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -32341,13 +33706,13 @@
         <v>50000077</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>1036</v>
+        <v>1071</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>1037</v>
+        <v>1072</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -32376,13 +33741,13 @@
         <v>50000078</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>1038</v>
+        <v>1073</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>1039</v>
+        <v>1074</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -32411,13 +33776,13 @@
         <v>50000079</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>1040</v>
+        <v>1075</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>1041</v>
+        <v>1076</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -32446,13 +33811,13 @@
         <v>50000080</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>1042</v>
+        <v>1077</v>
       </c>
       <c r="E85" s="9">
         <v>5</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>1043</v>
+        <v>1078</v>
       </c>
       <c r="G85" s="9">
         <v>1</v>
@@ -32481,13 +33846,13 @@
         <v>50000081</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>1044</v>
+        <v>1079</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>1045</v>
+        <v>1080</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -32516,13 +33881,13 @@
         <v>50000082</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1046</v>
+        <v>1081</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>1047</v>
+        <v>1082</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -32551,13 +33916,13 @@
         <v>50000083</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>1048</v>
+        <v>1083</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>1049</v>
+        <v>1084</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -32586,13 +33951,13 @@
         <v>50000084</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>1050</v>
+        <v>1085</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>1051</v>
+        <v>1086</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -32621,13 +33986,13 @@
         <v>50000085</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>1052</v>
+        <v>1087</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>1053</v>
+        <v>1088</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -32656,13 +34021,13 @@
         <v>50000086</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1054</v>
+        <v>1089</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>1055</v>
+        <v>1090</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -32691,13 +34056,13 @@
         <v>50000087</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1056</v>
+        <v>1091</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>1057</v>
+        <v>1092</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -32726,13 +34091,13 @@
         <v>50000088</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>1058</v>
+        <v>1093</v>
       </c>
       <c r="E93" s="9">
         <v>5</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>1059</v>
+        <v>1094</v>
       </c>
       <c r="G93" s="9">
         <v>1</v>
@@ -32761,13 +34126,13 @@
         <v>50000089</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>1060</v>
+        <v>1095</v>
       </c>
       <c r="E94" s="2">
         <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>1061</v>
+        <v>1096</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -32796,13 +34161,13 @@
         <v>50000090</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>1062</v>
+        <v>1097</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>1063</v>
+        <v>1098</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -32831,13 +34196,13 @@
         <v>50000091</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1064</v>
+        <v>1099</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>1065</v>
+        <v>1100</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -32866,13 +34231,13 @@
         <v>50000092</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1066</v>
+        <v>1101</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>1067</v>
+        <v>1102</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -32901,13 +34266,13 @@
         <v>50000093</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>1068</v>
+        <v>1103</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>1069</v>
+        <v>1104</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -32936,13 +34301,13 @@
         <v>50000094</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>1070</v>
+        <v>1105</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>1071</v>
+        <v>1106</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -32971,13 +34336,13 @@
         <v>50000095</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1072</v>
+        <v>1107</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>1073</v>
+        <v>1108</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -33006,13 +34371,13 @@
         <v>50000096</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>1074</v>
+        <v>1109</v>
       </c>
       <c r="E101" s="9">
         <v>5</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>1075</v>
+        <v>1110</v>
       </c>
       <c r="G101" s="9">
         <v>1</v>
@@ -33041,13 +34406,13 @@
         <v>50000097</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>1076</v>
+        <v>1111</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>1077</v>
+        <v>1112</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -33076,13 +34441,13 @@
         <v>50000098</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>1078</v>
+        <v>1113</v>
       </c>
       <c r="E103" s="2">
         <v>5</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>1079</v>
+        <v>1114</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -33111,13 +34476,13 @@
         <v>50000099</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>1080</v>
+        <v>1115</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>1081</v>
+        <v>1116</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -33146,13 +34511,13 @@
         <v>50000100</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>1082</v>
+        <v>1117</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>1083</v>
+        <v>1118</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -33181,13 +34546,13 @@
         <v>50000101</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>1084</v>
+        <v>1119</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>1085</v>
+        <v>1120</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -33216,13 +34581,13 @@
         <v>50000102</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>1086</v>
+        <v>1121</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>1087</v>
+        <v>1122</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -33251,13 +34616,13 @@
         <v>50000103</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>1088</v>
+        <v>1123</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>1089</v>
+        <v>1124</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -33286,13 +34651,13 @@
         <v>50000104</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>1090</v>
+        <v>1125</v>
       </c>
       <c r="E109" s="9">
         <v>5</v>
       </c>
       <c r="F109" s="9" t="s">
-        <v>1091</v>
+        <v>1126</v>
       </c>
       <c r="G109" s="9">
         <v>1</v>
@@ -33321,13 +34686,13 @@
         <v>50000105</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>1092</v>
+        <v>1127</v>
       </c>
       <c r="E110" s="2">
         <v>5</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>1093</v>
+        <v>1128</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
@@ -33356,13 +34721,13 @@
         <v>50000106</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>1094</v>
+        <v>1129</v>
       </c>
       <c r="E111" s="2">
         <v>5</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>1093</v>
+        <v>1128</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -33391,13 +34756,13 @@
         <v>50000107</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>1095</v>
+        <v>1130</v>
       </c>
       <c r="E112" s="2">
         <v>5</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>1093</v>
+        <v>1128</v>
       </c>
       <c r="G112" s="2">
         <v>1</v>
@@ -33426,13 +34791,13 @@
         <v>50000108</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>1096</v>
+        <v>1131</v>
       </c>
       <c r="E113" s="2">
         <v>5</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>1093</v>
+        <v>1128</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -33461,13 +34826,13 @@
         <v>50000109</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>1097</v>
+        <v>1132</v>
       </c>
       <c r="E114" s="2">
         <v>5</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>1093</v>
+        <v>1128</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -33496,13 +34861,13 @@
         <v>50000110</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>1098</v>
+        <v>1133</v>
       </c>
       <c r="E115" s="2">
         <v>5</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>1093</v>
+        <v>1128</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
@@ -33531,13 +34896,13 @@
         <v>50000111</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>1099</v>
+        <v>1134</v>
       </c>
       <c r="E116" s="8">
         <v>5</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1093</v>
+        <v>1128</v>
       </c>
       <c r="G116" s="8">
         <v>1</v>
@@ -33566,13 +34931,13 @@
         <v>50000112</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>1100</v>
+        <v>1135</v>
       </c>
       <c r="E117" s="9">
         <v>5</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G117" s="9">
         <v>1</v>
@@ -33601,13 +34966,13 @@
         <v>50000113</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>1102</v>
+        <v>1137</v>
       </c>
       <c r="E118" s="2">
         <v>5</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G118" s="2">
         <v>1</v>
@@ -33636,13 +35001,13 @@
         <v>50000114</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>1103</v>
+        <v>1138</v>
       </c>
       <c r="E119" s="2">
         <v>5</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G119" s="2">
         <v>1</v>
@@ -33671,13 +35036,13 @@
         <v>50000115</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>1104</v>
+        <v>1139</v>
       </c>
       <c r="E120" s="2">
         <v>5</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G120" s="2">
         <v>1</v>
@@ -33706,13 +35071,13 @@
         <v>50000116</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>1105</v>
+        <v>1140</v>
       </c>
       <c r="E121" s="2">
         <v>5</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G121" s="2">
         <v>1</v>
@@ -33741,13 +35106,13 @@
         <v>50000117</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>1106</v>
+        <v>1141</v>
       </c>
       <c r="E122" s="2">
         <v>5</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G122" s="2">
         <v>1</v>
@@ -33776,13 +35141,13 @@
         <v>50000118</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>1107</v>
+        <v>1142</v>
       </c>
       <c r="E123" s="2">
         <v>5</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G123" s="2">
         <v>1</v>
@@ -33811,13 +35176,13 @@
         <v>50000119</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>1108</v>
+        <v>1143</v>
       </c>
       <c r="E124" s="9">
         <v>5</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G124" s="9">
         <v>1</v>
@@ -33846,13 +35211,13 @@
         <v>50000120</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>1109</v>
+        <v>1144</v>
       </c>
       <c r="E125" s="2">
         <v>5</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G125" s="2">
         <v>1</v>
@@ -33881,13 +35246,13 @@
         <v>50000121</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>1110</v>
+        <v>1145</v>
       </c>
       <c r="E126" s="2">
         <v>5</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G126" s="2">
         <v>1</v>
@@ -33916,13 +35281,13 @@
         <v>50000122</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>1111</v>
+        <v>1146</v>
       </c>
       <c r="E127" s="2">
         <v>5</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G127" s="2">
         <v>1</v>
@@ -33951,13 +35316,13 @@
         <v>50000123</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>1112</v>
+        <v>1147</v>
       </c>
       <c r="E128" s="2">
         <v>5</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G128" s="2">
         <v>1</v>
@@ -33986,13 +35351,13 @@
         <v>50000124</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>1113</v>
+        <v>1148</v>
       </c>
       <c r="E129" s="2">
         <v>5</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G129" s="2">
         <v>1</v>
@@ -34021,13 +35386,13 @@
         <v>50000125</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>1114</v>
+        <v>1149</v>
       </c>
       <c r="E130" s="2">
         <v>5</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G130" s="2">
         <v>1</v>
@@ -34056,13 +35421,13 @@
         <v>50000126</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>1115</v>
+        <v>1150</v>
       </c>
       <c r="E131" s="9">
         <v>5</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G131" s="9">
         <v>1</v>
@@ -34091,13 +35456,13 @@
         <v>50000127</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>1116</v>
+        <v>1151</v>
       </c>
       <c r="E132" s="2">
         <v>5</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G132" s="2">
         <v>1</v>
@@ -34126,13 +35491,13 @@
         <v>50000128</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>1117</v>
+        <v>1152</v>
       </c>
       <c r="E133" s="2">
         <v>5</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G133" s="2">
         <v>1</v>
@@ -34161,13 +35526,13 @@
         <v>50000129</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>1118</v>
+        <v>1153</v>
       </c>
       <c r="E134" s="2">
         <v>5</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G134" s="2">
         <v>1</v>
@@ -34196,13 +35561,13 @@
         <v>50000130</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>1119</v>
+        <v>1154</v>
       </c>
       <c r="E135" s="2">
         <v>5</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G135" s="2">
         <v>1</v>
@@ -34231,13 +35596,13 @@
         <v>50000131</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>1120</v>
+        <v>1155</v>
       </c>
       <c r="E136" s="2">
         <v>5</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G136" s="2">
         <v>1</v>
@@ -34266,13 +35631,13 @@
         <v>50000132</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>1121</v>
+        <v>1156</v>
       </c>
       <c r="E137" s="2">
         <v>5</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="G137" s="2">
         <v>1</v>
@@ -34444,13 +35809,13 @@
         <v>60000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1122</v>
+        <v>1157</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -34479,13 +35844,13 @@
         <v>60000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1124</v>
+        <v>1159</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -34514,13 +35879,13 @@
         <v>60000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1125</v>
+        <v>1160</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -34549,13 +35914,13 @@
         <v>60000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1126</v>
+        <v>1161</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -34584,13 +35949,13 @@
         <v>60000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1127</v>
+        <v>1162</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -34619,13 +35984,13 @@
         <v>60000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1128</v>
+        <v>1163</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -34654,13 +36019,13 @@
         <v>60000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1129</v>
+        <v>1164</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -34689,13 +36054,13 @@
         <v>60000008</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1130</v>
+        <v>1165</v>
       </c>
       <c r="E13" s="8">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G13" s="8">
         <v>1</v>
@@ -34724,13 +36089,13 @@
         <v>60000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1131</v>
+        <v>1166</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -34759,13 +36124,13 @@
         <v>60000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1132</v>
+        <v>1167</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -34799,13 +36164,13 @@
         <v>60000011</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1133</v>
+        <v>1168</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -34834,13 +36199,13 @@
         <v>60000012</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1134</v>
+        <v>1169</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -34869,13 +36234,13 @@
         <v>60000013</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1135</v>
+        <v>1170</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -34904,13 +36269,13 @@
         <v>60000014</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1136</v>
+        <v>1171</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -34939,13 +36304,13 @@
         <v>60000015</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1137</v>
+        <v>1172</v>
       </c>
       <c r="E21" s="2">
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -34974,13 +36339,13 @@
         <v>60000016</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1138</v>
+        <v>1173</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -35009,13 +36374,13 @@
         <v>60000017</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1139</v>
+        <v>1174</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -35044,13 +36409,13 @@
         <v>60000018</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>1140</v>
+        <v>1175</v>
       </c>
       <c r="E24" s="8">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G24" s="8">
         <v>1</v>
@@ -35079,13 +36444,13 @@
         <v>60000019</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1141</v>
+        <v>1176</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -35114,13 +36479,13 @@
         <v>60000020</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1142</v>
+        <v>1177</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -35149,13 +36514,13 @@
         <v>60000021</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1143</v>
+        <v>1178</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -35184,13 +36549,13 @@
         <v>60000022</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1144</v>
+        <v>1179</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -35219,13 +36584,13 @@
         <v>60000023</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>1145</v>
+        <v>1180</v>
       </c>
       <c r="E29" s="8">
         <v>5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1123</v>
+        <v>1158</v>
       </c>
       <c r="G29" s="8">
         <v>1</v>
@@ -35264,13 +36629,13 @@
         <v>61000001</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1146</v>
+        <v>1181</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -35299,13 +36664,13 @@
         <v>61000002</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1148</v>
+        <v>1183</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -35334,13 +36699,13 @@
         <v>61000003</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1149</v>
+        <v>1184</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -35369,13 +36734,13 @@
         <v>61000004</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1150</v>
+        <v>1185</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -35404,13 +36769,13 @@
         <v>61000005</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1151</v>
+        <v>1186</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -35439,13 +36804,13 @@
         <v>61000006</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>1152</v>
+        <v>1187</v>
       </c>
       <c r="E37" s="2">
         <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -35474,13 +36839,13 @@
         <v>61000007</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1153</v>
+        <v>1188</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -35509,13 +36874,13 @@
         <v>61000008</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>1154</v>
+        <v>1189</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -35549,13 +36914,13 @@
         <v>61000009</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1155</v>
+        <v>1190</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -35584,13 +36949,13 @@
         <v>61000010</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1156</v>
+        <v>1191</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -35619,13 +36984,13 @@
         <v>61000011</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>1157</v>
+        <v>1192</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -35654,13 +37019,13 @@
         <v>61000012</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>1158</v>
+        <v>1193</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -35689,13 +37054,13 @@
         <v>61000013</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1159</v>
+        <v>1194</v>
       </c>
       <c r="E45" s="2">
         <v>5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -35724,13 +37089,13 @@
         <v>61000014</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>1160</v>
+        <v>1195</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -35759,13 +37124,13 @@
         <v>61000015</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1161</v>
+        <v>1196</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -35794,13 +37159,13 @@
         <v>61000016</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>1162</v>
+        <v>1197</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -35835,13 +37200,13 @@
         <v>61000017</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>1163</v>
+        <v>1198</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -35870,13 +37235,13 @@
         <v>61000018</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>1164</v>
+        <v>1199</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -35905,13 +37270,13 @@
         <v>61000019</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>1165</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -35940,13 +37305,13 @@
         <v>61000020</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>1166</v>
+        <v>1201</v>
       </c>
       <c r="E53" s="2">
         <v>5</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -35975,13 +37340,13 @@
         <v>61000021</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>1167</v>
+        <v>1202</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -36010,13 +37375,13 @@
         <v>61000022</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>1168</v>
+        <v>1203</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -36045,13 +37410,13 @@
         <v>61000023</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>1169</v>
+        <v>1204</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -36080,13 +37445,13 @@
         <v>61000024</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>1170</v>
+        <v>1205</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -36120,13 +37485,13 @@
         <v>61000025</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>1171</v>
+        <v>1206</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -36155,13 +37520,13 @@
         <v>61000026</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1172</v>
+        <v>1207</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -36190,13 +37555,13 @@
         <v>61000027</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>1173</v>
+        <v>1208</v>
       </c>
       <c r="E61" s="2">
         <v>5</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -36225,13 +37590,13 @@
         <v>61000028</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>1174</v>
+        <v>1209</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -36260,13 +37625,13 @@
         <v>61000029</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>1175</v>
+        <v>1210</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -36295,13 +37660,13 @@
         <v>61000030</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>1176</v>
+        <v>1211</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -36330,13 +37695,13 @@
         <v>61000031</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>1177</v>
+        <v>1212</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -36365,13 +37730,13 @@
         <v>61000032</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>1178</v>
+        <v>1213</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -36405,13 +37770,13 @@
         <v>61000033</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>1179</v>
+        <v>1214</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -36440,13 +37805,13 @@
         <v>61000034</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>1180</v>
+        <v>1215</v>
       </c>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -36475,13 +37840,13 @@
         <v>61000035</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>1181</v>
+        <v>1216</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -36510,13 +37875,13 @@
         <v>61000036</v>
       </c>
       <c r="D71" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E71" s="2">
+        <v>5</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>1182</v>
-      </c>
-      <c r="E71" s="2">
-        <v>5</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>1147</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -36545,13 +37910,13 @@
         <v>61000037</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>1183</v>
+        <v>1218</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -36580,13 +37945,13 @@
         <v>61000038</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>1184</v>
+        <v>1219</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -36615,13 +37980,13 @@
         <v>61000039</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>1185</v>
+        <v>1220</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -36650,13 +38015,13 @@
         <v>61000040</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>1186</v>
+        <v>1221</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -36690,13 +38055,13 @@
         <v>61000041</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>1187</v>
+        <v>1222</v>
       </c>
       <c r="E77" s="2">
         <v>5</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -36725,13 +38090,13 @@
         <v>61000042</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>1188</v>
+        <v>1223</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -36760,13 +38125,13 @@
         <v>61000043</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>1189</v>
+        <v>1224</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -36795,13 +38160,13 @@
         <v>61000044</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>1190</v>
+        <v>1225</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -36830,13 +38195,13 @@
         <v>61000045</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>1191</v>
+        <v>1226</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -36865,13 +38230,13 @@
         <v>61000046</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>1192</v>
+        <v>1227</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -36900,13 +38265,13 @@
         <v>61000047</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>1193</v>
+        <v>1228</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -36935,13 +38300,13 @@
         <v>61000048</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>1194</v>
+        <v>1229</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -36975,13 +38340,13 @@
         <v>61000049</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>1195</v>
+        <v>1230</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -37010,13 +38375,13 @@
         <v>61000050</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1196</v>
+        <v>1231</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -37045,13 +38410,13 @@
         <v>61000051</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>1197</v>
+        <v>1232</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -37080,13 +38445,13 @@
         <v>61000052</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>1198</v>
+        <v>1233</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -37115,13 +38480,13 @@
         <v>61000053</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>1199</v>
+        <v>1234</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -37150,13 +38515,13 @@
         <v>61000054</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1200</v>
+        <v>1235</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -37185,13 +38550,13 @@
         <v>61000055</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1201</v>
+        <v>1236</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -37220,13 +38585,13 @@
         <v>61000056</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>1202</v>
+        <v>1237</v>
       </c>
       <c r="E93" s="2">
         <v>5</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -37260,13 +38625,13 @@
         <v>61000057</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>1203</v>
+        <v>1238</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -37295,13 +38660,13 @@
         <v>61000058</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1204</v>
+        <v>1239</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -37330,13 +38695,13 @@
         <v>61000059</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1205</v>
+        <v>1240</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -37365,13 +38730,13 @@
         <v>61000060</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>1206</v>
+        <v>1241</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -37400,13 +38765,13 @@
         <v>61000061</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>1207</v>
+        <v>1242</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -37435,13 +38800,13 @@
         <v>61000062</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1208</v>
+        <v>1243</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -37470,13 +38835,13 @@
         <v>61000063</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>1209</v>
+        <v>1244</v>
       </c>
       <c r="E101" s="2">
         <v>5</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -37505,13 +38870,13 @@
         <v>61000064</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>1210</v>
+        <v>1245</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -37545,13 +38910,13 @@
         <v>61000065</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>1211</v>
+        <v>1246</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -37580,13 +38945,13 @@
         <v>61000066</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>1212</v>
+        <v>1247</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -37615,13 +38980,13 @@
         <v>61000067</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>1213</v>
+        <v>1248</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -37650,13 +39015,13 @@
         <v>61000068</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>1214</v>
+        <v>1249</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -37685,13 +39050,13 @@
         <v>61000069</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>1215</v>
+        <v>1250</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -37720,13 +39085,13 @@
         <v>61000070</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>1216</v>
+        <v>1251</v>
       </c>
       <c r="E109" s="2">
         <v>5</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -37755,13 +39120,13 @@
         <v>61000071</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>1217</v>
+        <v>1252</v>
       </c>
       <c r="E110" s="2">
         <v>5</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
@@ -37790,13 +39155,13 @@
         <v>61000072</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>1218</v>
+        <v>1253</v>
       </c>
       <c r="E111" s="2">
         <v>5</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -37830,13 +39195,13 @@
         <v>61000073</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>1219</v>
+        <v>1254</v>
       </c>
       <c r="E113" s="2">
         <v>5</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -37865,13 +39230,13 @@
         <v>61000074</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>1220</v>
+        <v>1255</v>
       </c>
       <c r="E114" s="2">
         <v>5</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -37900,13 +39265,13 @@
         <v>61000075</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>1221</v>
+        <v>1256</v>
       </c>
       <c r="E115" s="2">
         <v>5</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
@@ -37935,13 +39300,13 @@
         <v>61000076</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>1222</v>
+        <v>1257</v>
       </c>
       <c r="E116" s="2">
         <v>5</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
@@ -37970,13 +39335,13 @@
         <v>61000077</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>1223</v>
+        <v>1258</v>
       </c>
       <c r="E117" s="2">
         <v>5</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
@@ -38005,13 +39370,13 @@
         <v>61000078</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>1224</v>
+        <v>1259</v>
       </c>
       <c r="E118" s="2">
         <v>5</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G118" s="2">
         <v>1</v>
@@ -38040,13 +39405,13 @@
         <v>61000079</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>1225</v>
+        <v>1260</v>
       </c>
       <c r="E119" s="2">
         <v>5</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G119" s="2">
         <v>1</v>
@@ -38075,13 +39440,13 @@
         <v>61000080</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>1226</v>
+        <v>1261</v>
       </c>
       <c r="E120" s="2">
         <v>5</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>1147</v>
+        <v>1182</v>
       </c>
       <c r="G120" s="2">
         <v>1</v>
@@ -38252,13 +39617,13 @@
         <v>70000001</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1227</v>
+        <v>1262</v>
       </c>
       <c r="E6" s="2">
         <v>32</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -38287,13 +39652,13 @@
         <v>70000002</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1229</v>
+        <v>1264</v>
       </c>
       <c r="E7" s="2">
         <v>32</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -38322,13 +39687,13 @@
         <v>70000003</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1230</v>
+        <v>1265</v>
       </c>
       <c r="E8" s="2">
         <v>32</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -38357,13 +39722,13 @@
         <v>70000004</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1231</v>
+        <v>1266</v>
       </c>
       <c r="E9" s="2">
         <v>32</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -38392,13 +39757,13 @@
         <v>70000005</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1232</v>
+        <v>1267</v>
       </c>
       <c r="E10" s="2">
         <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -38427,13 +39792,13 @@
         <v>70000006</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1233</v>
+        <v>1268</v>
       </c>
       <c r="E11" s="2">
         <v>32</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -38462,13 +39827,13 @@
         <v>70000007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1234</v>
+        <v>1269</v>
       </c>
       <c r="E12" s="2">
         <v>32</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -38497,13 +39862,13 @@
         <v>70000008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1235</v>
+        <v>1270</v>
       </c>
       <c r="E13" s="2">
         <v>32</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -38532,13 +39897,13 @@
         <v>70000011</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1236</v>
+        <v>1271</v>
       </c>
       <c r="E14" s="2">
         <v>32</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -38567,13 +39932,13 @@
         <v>70000012</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1237</v>
+        <v>1272</v>
       </c>
       <c r="E15" s="2">
         <v>32</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -38602,13 +39967,13 @@
         <v>70000013</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1238</v>
+        <v>1273</v>
       </c>
       <c r="E16" s="2">
         <v>32</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -38637,13 +40002,13 @@
         <v>70000014</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1239</v>
+        <v>1274</v>
       </c>
       <c r="E17" s="2">
         <v>32</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -38672,13 +40037,13 @@
         <v>70000015</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1240</v>
+        <v>1275</v>
       </c>
       <c r="E18" s="2">
         <v>32</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -38707,13 +40072,13 @@
         <v>70000016</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1241</v>
+        <v>1276</v>
       </c>
       <c r="E19" s="2">
         <v>32</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -38742,13 +40107,13 @@
         <v>70000017</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1242</v>
+        <v>1277</v>
       </c>
       <c r="E20" s="2">
         <v>32</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -38777,13 +40142,13 @@
         <v>70000018</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1243</v>
+        <v>1278</v>
       </c>
       <c r="E21" s="2">
         <v>32</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -38812,13 +40177,13 @@
         <v>70000021</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1244</v>
+        <v>1279</v>
       </c>
       <c r="E22" s="2">
         <v>32</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -38847,13 +40212,13 @@
         <v>70000022</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1245</v>
+        <v>1280</v>
       </c>
       <c r="E23" s="2">
         <v>32</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -38882,13 +40247,13 @@
         <v>70000023</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1246</v>
+        <v>1281</v>
       </c>
       <c r="E24" s="2">
         <v>32</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -38917,13 +40282,13 @@
         <v>70000024</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1247</v>
+        <v>1282</v>
       </c>
       <c r="E25" s="2">
         <v>32</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -38952,13 +40317,13 @@
         <v>70000025</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1248</v>
+        <v>1283</v>
       </c>
       <c r="E26" s="2">
         <v>32</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -38987,13 +40352,13 @@
         <v>70000026</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>1249</v>
+        <v>1284</v>
       </c>
       <c r="E27" s="2">
         <v>32</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -39022,13 +40387,13 @@
         <v>70000027</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1250</v>
+        <v>1285</v>
       </c>
       <c r="E28" s="2">
         <v>32</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -39057,13 +40422,13 @@
         <v>70000028</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1251</v>
+        <v>1286</v>
       </c>
       <c r="E29" s="2">
         <v>32</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1228</v>
+        <v>1263</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
